--- a/out/Attention_Base_repeat_2_000002.xlsx
+++ b/out/Attention_Base_repeat_2_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.3</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.3</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.3</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.3</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.3</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.3</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.3</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.3</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.3</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.3</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.3</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.3</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.3</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.3</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.3</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.3</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.3</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.3</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.3</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.3</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.3</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.3</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.3</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.3</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.3</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.3</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.3</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>

--- a/out/Attention_Base_repeat_2_000002.xlsx
+++ b/out/Attention_Base_repeat_2_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention_Base_repeat_2_000002.xlsx
+++ b/out/Attention_Base_repeat_2_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002035166136920452</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.00958931352943182</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.00911934208124876</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.007270683534443378</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00764534343034029</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.007173684425652027</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.006104039028286934</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.007337223738431931</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01050258986651897</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01106314640492201</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01025181356817484</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.008960511535406113</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.008601869456470013</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.007962912321090698</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.007223060354590416</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.006652689538896084</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.006296360865235329</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.005928424187004566</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.005434026941657066</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.005053087137639523</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.004802879877388477</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.004395046271383762</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.003957410342991352</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.004992001689970493</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00563142541795969</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.00583267118781805</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.005989888682961464</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.006020719185471535</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.005811893381178379</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.005494172684848309</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.005259818397462368</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.004948974587023258</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.00465384591370821</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.004439066164195538</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.004484671168029308</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.004987659864127636</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.005422958172857761</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.005591033957898617</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.006098018027842045</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.00685842614620924</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.007759657688438892</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.008728471584618092</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0104040140286088</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.009608091786503792</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01352658774703741</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01458327658474445</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01595600135624409</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01614942401647568</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01711559295654297</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01605827361345291</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0175752080976963</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01833021827042103</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01961249113082886</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02014435082674026</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01981708779931068</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.02034599706530571</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02009979076683521</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01953407749533653</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01991156116127968</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02002734318375587</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01958741992712021</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02028559520840645</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02063729614019394</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02018960565328598</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02002493664622307</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0199963990598917</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02120092138648033</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02199669554829597</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0222473070025444</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02221822366118431</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02209915593266487</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02215996757149696</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02186588943004608</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02185817062854767</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02196942269802094</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02165080606937408</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02116929739713669</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02094468101859093</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02077624760568142</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02046981267631054</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02026437968015671</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01991292089223862</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01999123394489288</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01978914067149162</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01961740106344223</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.019491046667099</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0190136693418026</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01874066516757011</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01824339106678963</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01884718611836433</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01879875175654888</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01837504655122757</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01851155422627926</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01840171217918396</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01823297515511513</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01750769093632698</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01764634251594543</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01744105480611324</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01735833287239075</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0169411264359951</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01707009226083755</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01676316186785698</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01646483689546585</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01641305908560753</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01614784821867943</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01598878018558025</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01589586213231087</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01577438414096832</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01553317159414291</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01543951127678156</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.0150219053030014</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01497517060488462</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01483050361275673</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01482095196843147</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.01461681351065636</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01372223161160946</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01409553736448288</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01347185019403696</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01468046195805073</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01452844124287367</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01545397285372019</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01566226780414581</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01538762357085943</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01571953669190407</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01532989833503962</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
